--- a/engagement_survey_forms/003_employment_engagement_survey--engagement_survey_forms.xlsx
+++ b/engagement_survey_forms/003_employment_engagement_survey--engagement_survey_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>overall_happiness</t>
+          <t>overall_happiness_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>satisfaction_level</t>
+          <t>satisfaction_level_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>perception</t>
+          <t>perception_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Overall happiness</t>
+          <t>How would you describe your overall happiness with your work? (text)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Satisfaction level</t>
+          <t>What is your overall satisfaction level with your work?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,20 +640,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>What is your perception of your work experience?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,20 +663,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Overall happiness</t>
+          <t>Overall happiness (select one)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,20 +686,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Satisfaction level</t>
+          <t>Satisfaction level (select one)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,20 +709,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>Perception (select one)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,20 +732,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Overall happiness</t>
+          <t>Overall happiness (select multiple)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,20 +755,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Satisfaction level</t>
+          <t>Satisfaction level (select multiple)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,20 +778,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>Perception (select multiple)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Overall happiness</t>
+          <t>Overall happiness (date)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Satisfaction level</t>
+          <t>Satisfaction level (date)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,7 +837,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>Perception (date)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,7 +860,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Overall happiness</t>
+          <t>Overall happiness (time)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,7 +883,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Satisfaction level</t>
+          <t>Satisfaction level (time)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,7 +906,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>Perception (time)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,7 +929,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Overall happiness</t>
+          <t>Overall happiness (email)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,7 +952,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Satisfaction level</t>
+          <t>Satisfaction level (email)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,90 +975,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>perception_8</t>
+          <t>perception_7</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>Perception (email)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>overall_happiness_9</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Overall happiness</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>satisfaction_level_8</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Satisfaction level</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>perception_9</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Perception</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1079,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1103,510 +1034,510 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>overall_happiness_4_choices</t>
+          <t>overall_happiness_3_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_happy'}</t>
+          <t>very_happy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very happy'}</t>
+          <t>Very happy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>overall_happiness_4_choices</t>
+          <t>overall_happiness_3_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_happy'}</t>
+          <t>somewhat_happy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat happy'}</t>
+          <t>Somewhat happy</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>overall_happiness_4_choices</t>
+          <t>overall_happiness_3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>overall_happiness_4_choices</t>
+          <t>overall_happiness_3_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_not_happy'}</t>
+          <t>somewhat_not_happy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat not happy'}</t>
+          <t>Somewhat not happy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>overall_happiness_4_choices</t>
+          <t>overall_happiness_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_not_happy'}</t>
+          <t>very_not_happy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very not happy'}</t>
+          <t>Very not happy</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>satisfaction_level_4_choices</t>
+          <t>satisfaction_level_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>satisfaction_level_4_choices</t>
+          <t>satisfaction_level_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_good'}</t>
+          <t>somewhat_good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat good'}</t>
+          <t>Somewhat good</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>satisfaction_level_4_choices</t>
+          <t>satisfaction_level_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>satisfaction_level_4_choices</t>
+          <t>satisfaction_level_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_not_good'}</t>
+          <t>somewhat_not_good</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat not good'}</t>
+          <t>Somewhat not good</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>satisfaction_level_4_choices</t>
+          <t>satisfaction_level_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very_not_good'}</t>
+          <t>very_not_good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Very not good'}</t>
+          <t>Very not good</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>perception_4_choices</t>
+          <t>perception_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'very_positive'}</t>
+          <t>very_positive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Very positive'}</t>
+          <t>Very positive</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>perception_4_choices</t>
+          <t>perception_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_positive'}</t>
+          <t>somewhat_positive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat positive'}</t>
+          <t>Somewhat positive</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>perception_4_choices</t>
+          <t>perception_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>perception_4_choices</t>
+          <t>perception_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_negative'}</t>
+          <t>somewhat_negative</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat negative'}</t>
+          <t>Somewhat negative</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>perception_4_choices</t>
+          <t>perception_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'very_negative'}</t>
+          <t>very_negative</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Very negative'}</t>
+          <t>Very negative</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>overall_happiness_5_choices</t>
+          <t>overall_happiness_4_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'very_happy'}</t>
+          <t>very_happy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Very happy'}</t>
+          <t>Very happy</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>overall_happiness_5_choices</t>
+          <t>overall_happiness_4_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_happy'}</t>
+          <t>somewhat_happy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat happy'}</t>
+          <t>Somewhat happy</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>overall_happiness_5_choices</t>
+          <t>overall_happiness_4_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>overall_happiness_5_choices</t>
+          <t>overall_happiness_4_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_not_happy'}</t>
+          <t>somewhat_not_happy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat not happy'}</t>
+          <t>Somewhat not happy</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>overall_happiness_5_choices</t>
+          <t>overall_happiness_4_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'very_not_happy'}</t>
+          <t>very_not_happy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Very not happy'}</t>
+          <t>Very not happy</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>satisfaction_level_5_choices</t>
+          <t>satisfaction_level_4_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>satisfaction_level_5_choices</t>
+          <t>satisfaction_level_4_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_good'}</t>
+          <t>somewhat_good</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat good'}</t>
+          <t>Somewhat good</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>satisfaction_level_5_choices</t>
+          <t>satisfaction_level_4_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>satisfaction_level_5_choices</t>
+          <t>satisfaction_level_4_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_not_good'}</t>
+          <t>somewhat_not_good</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat not good'}</t>
+          <t>Somewhat not good</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>satisfaction_level_5_choices</t>
+          <t>satisfaction_level_4_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'very_not_good'}</t>
+          <t>very_not_good</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Very not good'}</t>
+          <t>Very not good</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>perception_5_choices</t>
+          <t>perception_4_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'very_positive'}</t>
+          <t>very_positive</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Very positive'}</t>
+          <t>Very positive</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>perception_5_choices</t>
+          <t>perception_4_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_positive'}</t>
+          <t>somewhat_positive</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat positive'}</t>
+          <t>Somewhat positive</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>perception_5_choices</t>
+          <t>perception_4_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>perception_5_choices</t>
+          <t>perception_4_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_negative'}</t>
+          <t>somewhat_negative</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat negative'}</t>
+          <t>Somewhat negative</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>perception_5_choices</t>
+          <t>perception_4_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'very_negative'}</t>
+          <t>very_negative</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Very negative'}</t>
+          <t>Very negative</t>
         </is>
       </c>
     </row>
